--- a/模型推理服务.xlsx
+++ b/模型推理服务.xlsx
@@ -3,22 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1470" yWindow="1470" windowWidth="16200" windowHeight="9848" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="等线"/>
       <family val="2"/>
@@ -48,6 +49,13 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -75,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -83,13 +91,31 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -435,24 +461,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="22.86328125" customWidth="1" min="1" max="1"/>
-    <col width="8.3984375" customWidth="1" min="2" max="2"/>
-    <col width="14.19921875" customWidth="1" min="3" max="3"/>
-    <col width="15.33203125" customWidth="1" min="4" max="4"/>
-    <col width="22.06640625" customWidth="1" min="5" max="5"/>
-    <col width="23.73046875" customWidth="1" min="6" max="6"/>
+    <col width="8.265625" customWidth="1" min="1" max="1"/>
+    <col width="40.59765625" customWidth="1" min="2" max="2"/>
+    <col width="8.3984375" customWidth="1" min="3" max="3"/>
+    <col width="14.19921875" customWidth="1" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" min="5" max="5"/>
+    <col width="37.19921875" customWidth="1" min="6" max="6"/>
+    <col width="40.59765625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.7" customHeight="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>任务编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>任务</t>
         </is>
@@ -477,1148 +504,1282 @@
           <t>交付物</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="34.35" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="2" ht="19.7" customHeight="1">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>一、新模型在华为显卡上部署验证</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="32.85" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="18.95" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>MiniMax-M2.5 在华为显卡上部署</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="10" t="n">
         <v>46104</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="10" t="n">
         <v>46105</v>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>能够双机部署</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="46.7" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="32.85" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>MiniMax-M2.5 在华为显卡上验证思考、工具调用功能</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>华为卡做多机部署测试，引入单排队已满，暂时无法进行</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32.85" customHeight="1">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Kimi-k2.5在华为显卡上部署</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>华为卡做多机部署测试，引入单排队已满，暂时无法进行</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32.85" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18.95" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Kimi-k2.5在华为显卡上验证思考、工具调用功能</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="32.85" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="18.95" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>设计新模型在华为显卡上的benchmark方案</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="34.35" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="19.7" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>二、新模型在海光显卡上部署验证</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="32.85" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="18.95" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>paddleocr-vl-1.5 在海光显卡上部署</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="10" t="n">
         <v>46106</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="10" t="n">
         <v>46115</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10" ht="32.85" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>paddleocr-vl-1.5 在海光显卡上验证OCR推理效果</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="46.7" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="32.85" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled及其V2版本引入</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="10" t="n">
         <v>46106</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="10" t="n">
         <v>46115</v>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>引入申请提单</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="46.7" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="32.85" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled在海光显卡上部署</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="6" t="n"/>
     </row>
     <row r="13" ht="18.95" customHeight="1">
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>039</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>qwen3-omni 在k100显卡上的部署验证</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>46136</v>
+      </c>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="34.35" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="18.95" customHeight="1">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="19.7" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>三、Cosyvoice2 语音模型华为显卡方案</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="129.95" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="74.45" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>解决 Cosyvoice 压测并发数过低的问题</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="10" t="n">
         <v>46097</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E16" s="10" t="n">
         <v>46105</v>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>目前使用 uvicorn 框架能够通过开启多个 worker 进行并发，每一个 worker 大概占用 7000M 显存，支持并发 1。后续需验证并发下语音质量情况以及一整张卡最大并发数上限。因本周有两天时间华为资源挪作测试使用，进度 + 2d。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32.85" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="18.95" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>联调 Cosyvoice 的并发脚本，验证是否能够支撑</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D17" s="10" t="n">
         <v>46106</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E17" s="10" t="n">
         <v>46112</v>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>中间华为机器用作其它测试工作</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32.85" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="18.95" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>012</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Cosyvoice2 在中文男声下会出现混合音调的问题</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="10" t="n">
         <v>46132</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E18" s="10" t="n">
         <v>46157</v>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>尝试使用自定义生成音色 pt 文件修复此问题。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="34.35" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19" ht="19.7" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>四、不同参数模型在海光 BW100上性能测试</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-    </row>
-    <row r="19" ht="32.85" customHeight="1">
-      <c r="A19" t="inlineStr">
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="18.95" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>013</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>32B 以下模型在海光 BW100 显卡部署</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D20" s="10" t="n">
         <v>46118</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E20" s="10" t="n">
         <v>46122</v>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>测试 BW100 在 32B 以下参数的模型性能；</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32.85" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="18.95" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>014</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>32B 以上模型在海光 BW100 显卡部署</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>测试 BW100 在 32B 以上参数的模型性能；</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32.85" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="32.85" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>32B 以上参数模型在海光 BW100 显卡上的性能测试</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="32.85" customHeight="1">
-      <c r="A22" t="inlineStr">
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="32.85" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>016</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>32B 以下参数模型在海光 BW100 显卡上的性能测试</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D23" s="10" t="n">
         <v>46127</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E23" s="10" t="n">
         <v>46133</v>
       </c>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="34.35" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="6" t="n"/>
+    </row>
+    <row r="24" ht="19.7" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>五、模型在海光显卡上的推理加速方案</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="46.7" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="32.85" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>017</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>测试环境缓存优化（前缀、字符串、语义）方案测试数据获取</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D25" s="10" t="n">
         <v>46104</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E25" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>性能对比图、性能测试文档</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>测试环境开启后收集数据，并形成文档</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32.85" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="18.95" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>018</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>设计模型LMCache加速在海光显卡上的验证方案</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E26" s="10" t="n">
         <v>46122</v>
       </c>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>同步调研SGLang等其它主流推理引擎实现方案</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32.85" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="18.95" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>测试环境显卡上LMCache方案验证</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D27" s="10" t="n">
         <v>46125</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E27" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="32.85" customHeight="1">
-      <c r="A27" t="inlineStr">
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="32.85" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>设计海光显卡上的 PD 分离方案</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E28" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>单验证软件方案是否可用、后续硬件到位再继续做验证</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32.85" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="18.95" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>引入海光显卡上PD分离相关的依赖</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D29" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E29" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="32.85" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="18.95" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>022</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>测试环境验证海光显卡上PD分离方案效果</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="34.35" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="18.95" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>模型kvcache环境加速方案-性能测试</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="19.7" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>六、模型在PPU上的性能验证</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="32.85" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="18.95" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>qwen3-32B和qwen3.5-35B模型在PPU显卡部署</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D33" s="10" t="n">
         <v>46125</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E33" s="10" t="n">
         <v>46129</v>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="32.85" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="18.95" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>024</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>qwen3.5-122B模型在PPU显卡部署</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D34" s="10" t="n">
         <v>46125</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E34" s="10" t="n">
         <v>46129</v>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="32.85" customHeight="1">
-      <c r="A33" t="inlineStr">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="18.95" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>025</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>qwen3-tts和qwen3-asr模型在PPU显卡部署</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D35" s="10" t="n">
         <v>46125</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E35" s="10" t="n">
         <v>46129</v>
       </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="32.85" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="18.95" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>026</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>32B参数模型在PPU上进行性能压测</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D36" s="10" t="n">
         <v>46132</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E36" s="10" t="n">
         <v>46136</v>
       </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="32.85" customHeight="1">
-      <c r="A35" t="inlineStr">
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="18.95" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>027</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>高参数模型在PPU上进行性能压测</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D37" s="10" t="n">
         <v>46132</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E37" s="10" t="n">
         <v>46136</v>
       </c>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="19.7" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="18.95" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>glm5/cosyvoice/sensevoice在ppu上的部署验证</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="19.7" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>七、技术支撑</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="32.85" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="18.95" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>028</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>制作vllm0.11.0推理引擎镜像，增加可观测组件</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D40" s="10" t="n">
         <v>46106</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E40" s="10" t="n">
         <v>46112</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>推理引擎镜像vllm0.11.0-opentelemetry</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>需求方：可观测；</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="32.85" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="41" ht="32.85" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>029</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>开测环境模型更换推理引擎vllm0.11.0-opentelemetry</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D41" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E41" s="10" t="n">
         <v>46157</v>
       </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>需求方：可观测；</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19.7" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="42" ht="18.95" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>业务维度模型数据集评测方案 - 初版草稿</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="18.95" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>qwen3.6/glm5.1/minimax2.7引入</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="19.7" customHeight="1">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>八、外部</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="32.85" customHeight="1">
-      <c r="A40" t="inlineStr">
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="32.85" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>030</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>AI模型网关中AI模型供应商对Reranker模型的支持</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D45" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E45" s="10" t="n">
         <v>46171</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>higress社区有无方案</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="32.85" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="G45" s="6" t="n"/>
+    </row>
+    <row r="46" ht="18.95" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>031</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>AI模型网关模型接入模型服务流程</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D46" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E46" s="10" t="n">
         <v>46171</v>
       </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="18.95" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="6" t="n"/>
+    </row>
+    <row r="47" ht="18.95" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>032</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>AI模型网关升级流程</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D47" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E47" s="10" t="n">
         <v>46171</v>
       </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-    </row>
-    <row r="43" ht="18.95" customHeight="1">
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="46.7" customHeight="1">
-      <c r="B44" s="3" t="inlineStr">
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="18.95" customHeight="1">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="6" t="n"/>
+    </row>
+    <row r="49" ht="19.7" customHeight="1">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="18.95" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="18.95" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>033</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>完成MiniMax-M2.5在华为显卡上的部署</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D50" s="10" t="n">
         <v>46104</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E50" s="10" t="n">
         <v>46115</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>MiniMax-M2.5部署文档</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>延期：华为卡多机部署测试占用，引入单排队已满</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19.7" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="51" ht="18.95" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>034</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>完成Kimi-k2.5在华为显卡上的部署</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D51" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E51" s="10" t="n">
         <v>46127</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Kimi-k2.5部署文档</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n"/>
-    </row>
-    <row r="47" ht="32.85" customHeight="1">
-      <c r="A47" t="inlineStr">
+      <c r="G51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="32.85" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>035</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>完成不同参数量模型在海光BW100显卡上的性能测试</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D52" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E52" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>性能测试文档</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="32.85" customHeight="1">
-      <c r="A48" t="inlineStr">
+      <c r="G52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="18.95" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>036</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>完成海光的LMCache方案验证</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D53" s="10" t="n">
         <v>46113</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E53" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>性能对比图</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n"/>
-    </row>
-    <row r="49" ht="32.85" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="G53" s="6" t="n"/>
+    </row>
+    <row r="54" ht="18.95" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>037</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>完成海光的PD分离方案验证（单纯软件层面）</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>未启动</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D54" s="10" t="n">
         <v>46143</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E54" s="10" t="n">
         <v>46172</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>性能对比图</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n"/>
-    </row>
-    <row r="50" ht="32.85" customHeight="1">
-      <c r="A50" t="inlineStr">
+      <c r="G54" s="6" t="n"/>
+    </row>
+    <row r="55" ht="18.95" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>038</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>完成ASR/TTS模型在华为显卡上的适配工作</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D55" s="10" t="n">
         <v>46050</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E55" s="10" t="n">
         <v>46326</v>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>TTS/ASR部署手册、TTS/ASR性能测试文档</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="32.85" customHeight="1"/>
-    <row r="52" ht="32.85" customHeight="1"/>
+      <c r="G55" s="6" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/模型推理服务.xlsx
+++ b/模型推理服务.xlsx
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -1553,7 +1553,11 @@
         <v>46171</v>
       </c>
       <c r="F46" s="3" t="n"/>
-      <c r="G46" s="6" t="n"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>准备交接文档给网关小组</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18.95" customHeight="1">
       <c r="A47" s="4" t="inlineStr">

--- a/模型推理服务.xlsx
+++ b/模型推理服务.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="8.265625" customWidth="1" min="1" max="1"/>
@@ -645,155 +645,164 @@
       <c r="G7" s="6" t="n"/>
     </row>
     <row r="8" ht="19.7" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>升级glm4.7的推理引擎版本</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>解决流式推理时思考不显示的问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18.95" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>二、新模型在海光显卡上部署验证</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="18.95" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>paddleocr-vl-1.5 在海光显卡上部署</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>46115</v>
-      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="6" t="n"/>
     </row>
     <row r="10" ht="32.85" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>006</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>paddleocr-vl-1.5 在海光显卡上验证OCR推理效果</t>
+          <t>paddleocr-vl-1.5 在海光显卡上部署</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>46115</v>
+      </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="6" t="n"/>
     </row>
     <row r="11" ht="32.85" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>008</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled及其V2版本引入</t>
+          <t>paddleocr-vl-1.5 在海光显卡上验证OCR推理效果</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>46115</v>
-      </c>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>引入申请提单</t>
-        </is>
-      </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12" ht="32.85" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>008</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled在海光显卡上部署</t>
+          <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled及其V2版本引入</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>46115</v>
+      </c>
       <c r="F12" s="3" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>引入申请提单</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18.95" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Qwen3.5-27B-Claude-4.6-Opus-Reasoning-Distilled在海光显卡上部署</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="18.95" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>039</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>qwen3-omni 在k100显卡上的部署验证</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D14" s="11" t="n">
         <v>46132</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E14" s="11" t="n">
         <v>46136</v>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="18.95" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="8" t="n"/>
     </row>
     <row r="15" ht="19.7" customHeight="1">
       <c r="A15" s="4" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>三、Cosyvoice2 语音模型华为显卡方案</t>
-        </is>
-      </c>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
@@ -801,43 +810,27 @@
       <c r="G15" s="6" t="n"/>
     </row>
     <row r="16" ht="74.45" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>010</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>解决 Cosyvoice 压测并发数过低的问题</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>46097</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>46105</v>
-      </c>
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>三、Cosyvoice2 语音模型华为显卡方案</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>目前使用 uvicorn 框架能够通过开启多个 worker 进行并发，每一个 worker 大概占用 7000M 显存，支持并发 1。后续需验证并发下语音质量情况以及一整张卡最大并发数上限。因本周有两天时间华为资源挪作测试使用，进度 + 2d。</t>
-        </is>
-      </c>
+      <c r="G16" s="6" t="n"/>
     </row>
     <row r="17" ht="18.95" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>010</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>联调 Cosyvoice 的并发脚本，验证是否能够支撑</t>
+          <t>解决 Cosyvoice 压测并发数过低的问题</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -846,123 +839,127 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>46106</v>
+        <v>46097</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>中间华为机器用作其它测试工作</t>
+          <t>目前使用 uvicorn 框架能够通过开启多个 worker 进行并发，每一个 worker 大概占用 7000M 显存，支持并发 1。后续需验证并发下语音质量情况以及一整张卡最大并发数上限。因本周有两天时间华为资源挪作测试使用，进度 + 2d。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18.95" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Cosyvoice2 在中文男声下会出现混合音调的问题</t>
+          <t>联调 Cosyvoice 的并发脚本，验证是否能够支撑</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>46157</v>
+        <v>46112</v>
       </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
+          <t>中间华为机器用作其它测试工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.7" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Cosyvoice2 在中文男声下会出现混合音调的问题</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
           <t>尝试使用自定义生成音色 pt 文件修复此问题。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19.7" customHeight="1">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+    <row r="20" ht="18.95" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>四、不同参数模型在海光 BW100上性能测试</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="18.95" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>013</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>32B 以下模型在海光 BW100 显卡部署</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>46118</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>46122</v>
-      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>测试 BW100 在 32B 以下参数的模型性能；</t>
-        </is>
-      </c>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21" ht="18.95" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>32B 以上模型在海光 BW100 显卡部署</t>
+          <t>32B 以下模型在海光 BW100 显卡部署</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>46122</v>
+      </c>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>测试 BW100 在 32B 以上参数的模型性能；</t>
+          <t>测试 BW100 在 32B 以下参数的模型性能；</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32.85" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>014</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>32B 以上参数模型在海光 BW100 显卡上的性能测试</t>
+          <t>32B 以上模型在海光 BW100 显卡部署</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -973,171 +970,167 @@
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>测试 BW100 在 32B 以上参数的模型性能；</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32.85" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>32B 以下参数模型在海光 BW100 显卡上的性能测试</t>
+          <t>32B 以上参数模型在海光 BW100 显卡上的性能测试</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>46133</v>
-      </c>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="6" t="n"/>
     </row>
     <row r="24" ht="19.7" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>五、模型在海光显卡上的推理加速方案</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>32B 以下参数模型在海光 BW100 显卡上的性能测试</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>46133</v>
+      </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="6" t="n"/>
     </row>
     <row r="25" ht="32.85" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>测试环境缓存优化（前缀、字符串、语义）方案测试数据获取</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>46142</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>性能对比图、性能测试文档</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>测试环境开启后收集数据，并形成文档</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>五、模型在海光显卡上的推理加速方案</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26" ht="18.95" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>设计模型LMCache加速在海光显卡上的验证方案</t>
+          <t>测试环境缓存优化（前缀、字符串、语义）方案测试数据获取</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>46122</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
+        <v>46142</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>性能对比图、性能测试文档</t>
+        </is>
+      </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>同步调研SGLang等其它主流推理引擎实现方案</t>
+          <t>测试环境开启后收集数据，并形成文档</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18.95" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>测试环境显卡上LMCache方案验证</t>
+          <t>设计模型LMCache加速在海光显卡上的验证方案</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>46142</v>
+        <v>46122</v>
       </c>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>同步调研SGLang等其它主流推理引擎实现方案</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="32.85" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>设计海光显卡上的 PD 分离方案</t>
+          <t>测试环境显卡上LMCache方案验证</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>46142</v>
       </c>
       <c r="F28" s="3" t="n"/>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>单验证软件方案是否可用、后续硬件到位再继续做验证</t>
-        </is>
-      </c>
+      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29" ht="18.95" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>020</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>引入海光显卡上PD分离相关的依赖</t>
+          <t>设计海光显卡上的 PD 分离方案</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1152,17 +1145,21 @@
         <v>46142</v>
       </c>
       <c r="F29" s="3" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>单验证软件方案是否可用、后续硬件到位再继续做验证</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18.95" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>测试环境验证海光显卡上PD分离方案效果</t>
+          <t>引入海光显卡上PD分离相关的依赖</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1170,83 +1167,83 @@
           <t>未启动</t>
         </is>
       </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
+      <c r="D30" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>46142</v>
+      </c>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="6" t="n"/>
     </row>
     <row r="31" ht="18.95" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>022</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>测试环境验证海光显卡上PD分离方案效果</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="19.7" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>041</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>模型kvcache环境加速方案-性能测试</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D32" s="11" t="n">
         <v>46132</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E32" s="11" t="n">
         <v>46136</v>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="19.7" customHeight="1">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="18.95" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>六、模型在PPU上的性能验证</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="18.95" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>023</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>qwen3-32B和qwen3.5-35B模型在PPU显卡部署</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>46125</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>46129</v>
-      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="6" t="n"/>
     </row>
     <row r="34" ht="18.95" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>qwen3.5-122B模型在PPU显卡部署</t>
+          <t>qwen3-32B和qwen3.5-35B模型在PPU显卡部署</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1266,12 +1263,12 @@
     <row r="35" ht="18.95" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>024</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>qwen3-tts和qwen3-asr模型在PPU显卡部署</t>
+          <t>qwen3.5-122B模型在PPU显卡部署</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1291,24 +1288,24 @@
     <row r="36" ht="18.95" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>026</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>32B参数模型在PPU上进行性能压测</t>
+          <t>qwen3-tts和qwen3-asr模型在PPU显卡部署</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>46136</v>
+        <v>46129</v>
       </c>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="6" t="n"/>
@@ -1316,12 +1313,12 @@
     <row r="37" ht="18.95" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>027</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>高参数模型在PPU上进行性能压测</t>
+          <t>32B参数模型在PPU上进行性能压测</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1341,97 +1338,93 @@
     <row r="38" ht="18.95" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>高参数模型在PPU上进行性能压测</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="19.7" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>040</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>glm5/cosyvoice/sensevoice在ppu上的部署验证</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D39" s="11" t="n">
         <v>46132</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E39" s="11" t="n">
         <v>46136</v>
       </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="8" t="n"/>
-    </row>
-    <row r="39" ht="19.7" customHeight="1">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="18.95" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>七、技术支撑</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="6" t="n"/>
-    </row>
-    <row r="40" ht="18.95" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>028</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>制作vllm0.11.0推理引擎镜像，增加可观测组件</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>46112</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>推理引擎镜像vllm0.11.0-opentelemetry</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>需求方：可观测；</t>
-        </is>
-      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="6" t="n"/>
     </row>
     <row r="41" ht="32.85" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>开测环境模型更换推理引擎vllm0.11.0-opentelemetry</t>
+          <t>制作vllm0.11.0推理引擎镜像，增加可观测组件</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>46157</v>
-      </c>
-      <c r="F41" s="3" t="n"/>
+        <v>46112</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>推理引擎镜像vllm0.11.0-opentelemetry</t>
+        </is>
+      </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
           <t>需求方：可观测；</t>
@@ -1441,37 +1434,41 @@
     <row r="42" ht="18.95" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>042</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>业务维度模型数据集评测方案 - 初版草稿</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+          <t>029</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>开测环境模型更换推理引擎vllm0.11.0-opentelemetry</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n">
-        <v>46132</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>46136</v>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="8" t="n"/>
+      <c r="D42" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>需求方：可观测；</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18.95" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>042</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>qwen3.6/glm5.1/minimax2.7引入</t>
+          <t>业务维度模型数据集评测方案 - 初版草稿</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1489,61 +1486,57 @@
       <c r="G43" s="8" t="n"/>
     </row>
     <row r="44" ht="19.7" customHeight="1">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>qwen3.6/glm5.1/minimax2.7引入</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="8" t="n"/>
+    </row>
+    <row r="45" ht="32.85" customHeight="1">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>八、外部</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="6" t="n"/>
-    </row>
-    <row r="45" ht="32.85" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>030</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>AI模型网关中AI模型供应商对Reranker模型的支持</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>未启动</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>46171</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>higress社区有无方案</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="3" t="n"/>
       <c r="G45" s="6" t="n"/>
     </row>
     <row r="46" ht="18.95" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>AI模型网关模型接入模型服务流程</t>
+          <t>AI模型网关中AI模型供应商对Reranker模型的支持</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未启动</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -1552,27 +1545,27 @@
       <c r="E46" s="10" t="n">
         <v>46171</v>
       </c>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>准备交接文档给网关小组</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>higress社区有无方案</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n"/>
     </row>
     <row r="47" ht="18.95" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>AI模型网关升级流程</t>
+          <t>AI模型网关模型接入模型服务流程</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
@@ -1582,24 +1575,40 @@
         <v>46171</v>
       </c>
       <c r="F47" s="3" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>准备交接文档给网关小组</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="18.95" customHeight="1">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>AI模型网关升级流程</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>46171</v>
+      </c>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="6" t="n"/>
     </row>
     <row r="49" ht="19.7" customHeight="1">
       <c r="A49" s="4" t="n"/>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="n"/>
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="10" t="n"/>
       <c r="E49" s="10" t="n"/>
@@ -1607,92 +1616,76 @@
       <c r="G49" s="6" t="n"/>
     </row>
     <row r="50" ht="18.95" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>033</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>完成MiniMax-M2.5在华为显卡上的部署</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>46115</v>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>MiniMax-M2.5部署文档</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>延期：华为卡多机部署测试占用，引入单排队已满</t>
-        </is>
-      </c>
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="6" t="n"/>
     </row>
     <row r="51" ht="18.95" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>完成Kimi-k2.5在华为显卡上的部署</t>
+          <t>完成MiniMax-M2.5在华为显卡上的部署</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>46127</v>
+        <v>46115</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Kimi-k2.5部署文档</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="n"/>
+          <t>MiniMax-M2.5部署文档</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>延期：华为卡多机部署测试占用，引入单排队已满</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="32.85" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>035</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>完成不同参数量模型在海光BW100显卡上的性能测试</t>
+          <t>完成Kimi-k2.5在华为显卡上的部署</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>未启动</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
         <v>46113</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>46142</v>
+        <v>46127</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>性能测试文档</t>
+          <t>Kimi-k2.5部署文档</t>
         </is>
       </c>
       <c r="G52" s="6" t="n"/>
@@ -1700,12 +1693,12 @@
     <row r="53" ht="18.95" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>完成海光的LMCache方案验证</t>
+          <t>完成不同参数量模型在海光BW100显卡上的性能测试</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -1721,7 +1714,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>性能对比图</t>
+          <t>性能测试文档</t>
         </is>
       </c>
       <c r="G53" s="6" t="n"/>
@@ -1729,24 +1722,24 @@
     <row r="54" ht="18.95" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>完成海光的PD分离方案验证（单纯软件层面）</t>
+          <t>完成海光的LMCache方案验证</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>未启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>46172</v>
+        <v>46142</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -1758,31 +1751,60 @@
     <row r="55" ht="18.95" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>完成海光的PD分离方案验证（单纯软件层面）</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>未启动</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>46172</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>性能对比图</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>038</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>完成ASR/TTS模型在华为显卡上的适配工作</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n">
+      <c r="D56" s="10" t="n">
         <v>46050</v>
       </c>
-      <c r="E55" s="10" t="n">
+      <c r="E56" s="10" t="n">
         <v>46326</v>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>TTS/ASR部署手册、TTS/ASR性能测试文档</t>
         </is>
       </c>
-      <c r="G55" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
